--- a/AAII_Financials/Quarterly/SYANY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SYANY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="92">
   <si>
     <t>SYANY</t>
   </si>
@@ -656,80 +656,88 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -772,8 +780,14 @@
       <c r="P8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -816,8 +830,14 @@
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -860,8 +880,14 @@
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,8 +904,10 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -922,8 +950,14 @@
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,8 +1000,14 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1010,8 +1050,14 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1054,8 +1100,14 @@
       <c r="P15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,8 +1121,10 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1113,8 +1167,14 @@
       <c r="P17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1157,8 +1217,14 @@
       <c r="P18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,8 +1241,10 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1219,8 +1287,14 @@
       <c r="P20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1263,8 +1337,14 @@
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1307,8 +1387,14 @@
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1351,8 +1437,14 @@
       <c r="P23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1395,8 +1487,14 @@
       <c r="P24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,8 +1537,14 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1483,8 +1587,14 @@
       <c r="P26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1527,8 +1637,14 @@
       <c r="P27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1687,14 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1737,14 @@
       <c r="P29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1787,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,8 +1837,14 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1747,8 +1887,14 @@
       <c r="P32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1791,8 +1937,14 @@
       <c r="P33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,8 +1987,14 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1879,57 +2037,69 @@
       <c r="P35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2116,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,140 +2136,160 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4898100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2726900</v>
+      </c>
+      <c r="F41" s="3">
         <v>3206000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>674700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>542400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>666200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>522200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>285100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>159900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>144800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1023800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1585500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1252200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>799600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1235600</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>7822000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>7655000</v>
+      </c>
+      <c r="F42" s="3">
         <v>4013300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>7897000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>8011500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>7676900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>3834700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>8008800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>5597800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>6408200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>3196500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>4926300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>5059400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>4851800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>2449100</v>
       </c>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2747400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2968100</v>
+      </c>
+      <c r="F43" s="3">
         <v>2419300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>3244500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>2223700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>2216800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>2058300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>2606600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2874500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2361000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>2773000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>2795800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>2545300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>2640800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>3275600</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2140,228 +2332,264 @@
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>79500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>87500</v>
+      </c>
+      <c r="F45" s="3">
         <v>95100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>39700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>47200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>46700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>51800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>55600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>64100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>61600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>60200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>52200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>44100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>38600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>28000</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>15747000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>13632800</v>
+      </c>
+      <c r="F46" s="3">
         <v>9984800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>11949900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>10947500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>10704600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>6561600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>11044200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>8791100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>9057700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>7158300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>9465400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>9017600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>8466500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>7114500</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>7593700</v>
+      </c>
+      <c r="E47" s="3">
+        <v>8291100</v>
+      </c>
+      <c r="F47" s="3">
         <v>12007100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>1231300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>2687200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>1232400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>4876100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>816600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>3402600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>2529600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>5591800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>2682800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>2913200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>2712000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>4830900</v>
       </c>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>539600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>457100</v>
+      </c>
+      <c r="F48" s="3">
         <v>571500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>200300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>201800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>186900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>181200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>183500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>177400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>180100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>187200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>173900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>183100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>183900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>183300</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1387100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1404200</v>
+      </c>
+      <c r="F49" s="3">
         <v>1434900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>62200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>63600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>59700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>58400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>64300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>45800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>46700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>48800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>48200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>51000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>51900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>52300</v>
       </c>
     </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2632,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,52 +2682,64 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7938400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>7455400</v>
+      </c>
+      <c r="F52" s="3">
         <v>7706800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>4356500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>4233700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>3804000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>3748900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>3903400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>3670100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>3513000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>3396600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>3069500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>3177200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>3078900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>2959300</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,52 +2782,64 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>55165500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>53209300</v>
+      </c>
+      <c r="F54" s="3">
         <v>53758300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>30880800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>31147900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>27763200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>26885600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>28363700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>27477600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>26601500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>27449900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>25676500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>26279400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>25447500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>25764100</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2856,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,272 +2876,310 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>41176800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>40011600</v>
+      </c>
+      <c r="F57" s="3">
         <v>40323000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>22766900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>23244000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>20723800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>19736800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>20834600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>19429400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>18959300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>19464700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>18017300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>18052400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>17639800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>18246000</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1720800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1552900</v>
+      </c>
+      <c r="F58" s="3">
         <v>1510200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1553200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1490900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1332800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1562200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1549300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1723200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1960000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>2118000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1986300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>2106300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>2051000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>1829900</v>
       </c>
     </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>121900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>121300</v>
+      </c>
+      <c r="F59" s="3">
         <v>95000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>44500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>88300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>87700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>50000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>150300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>140900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>83200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>68700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>113300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>85500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>89100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>93100</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>43107400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>41743400</v>
+      </c>
+      <c r="F60" s="3">
         <v>41991500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>24393900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>24890700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>22192600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>21380300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>22589500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>21376900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>21065000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>21684600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>20170100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>20293400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>19813700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>20196300</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4441500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>3733800</v>
+      </c>
+      <c r="F61" s="3">
         <v>3920700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2682400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>2099400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1935400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1848700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1991700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2413300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1888700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>1820900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>2045400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>2107900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>2103000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>2062800</v>
       </c>
     </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1898200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>2057600</v>
+      </c>
+      <c r="F62" s="3">
         <v>1795800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1341000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>1620600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>1451400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>1437800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1441000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1486900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1495900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1606500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>1305500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>1749600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>1523300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>1493700</v>
       </c>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3222,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3272,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,52 +3322,64 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>49578200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>47667700</v>
+      </c>
+      <c r="F66" s="3">
         <v>47839800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>28446600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>28643900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>25608600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>24694400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>26025300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>25279900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>24453000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>25114600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>23532300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>24153700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>23442700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>23755400</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3396,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3442,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3492,14 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3206,8 +3542,14 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,52 +3592,64 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5147000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>5088000</v>
+      </c>
+      <c r="F72" s="3">
         <v>5435900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>2180800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>2132100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>1929800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1973600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>2118000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>1985100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>1933300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>2112900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>1931500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>1905100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>1784200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>1789500</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3692,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3742,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,52 +3792,64 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5587200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>5535800</v>
+      </c>
+      <c r="F76" s="3">
         <v>5911800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>2427500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2497800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>2149300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>2185300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>2332100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>2192300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>2143300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>2329600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>2138600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>2120400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1999700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>2003200</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,57 +3892,69 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3607,8 +3997,14 @@
       <c r="P81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,52 +4021,60 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F83" s="3">
         <v>1800</v>
-      </c>
-      <c r="E83" s="3">
-        <v>4200</v>
-      </c>
-      <c r="F83" s="3">
-        <v>4200</v>
       </c>
       <c r="G83" s="3">
         <v>4200</v>
       </c>
       <c r="H83" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I83" s="3">
+        <v>4200</v>
+      </c>
+      <c r="J83" s="3">
         <v>-2500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>6100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>4400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>4700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>2000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>4100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>4400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>5200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +4117,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +4167,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4217,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4267,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4317,64 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>573300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-362400</v>
+      </c>
+      <c r="F89" s="3">
         <v>739500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>161800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-822300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>195500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>5700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>743800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-851800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-276400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-1070100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-152000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>285700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>592100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-806800</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,52 +4391,60 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="F91" s="3">
         <v>-8800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-1900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-1600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-8600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-1300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-2400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-9300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-1600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-1500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-1200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-7300</v>
       </c>
     </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4487,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,52 +4537,64 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F94" s="3">
         <v>1960900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-1400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>3800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-7100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-53200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-2200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>1900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-8200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-2100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-1200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>14900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-31500</v>
       </c>
     </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,52 +4611,60 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>4</v>
+      <c r="D96" s="3">
+        <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
+        <v>332900</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>201500</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>243000</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>139900</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4707,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4757,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,52 +4807,64 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1690600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>64000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-255900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-10500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>647200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-19600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>216300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-577000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>837600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-497100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>378600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>534600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>180300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-1019800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>121000</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4409,48 +4907,60 @@
       <c r="P101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2258900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-296200</v>
+      </c>
+      <c r="F102" s="3">
         <v>2444500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>149900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-171300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>176200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>214900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>113500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-16400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-771600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-699700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>380400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>464800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-412900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-717200</v>
       </c>
     </row>
